--- a/artfynd/A 17482-2026 artfynd.xlsx
+++ b/artfynd/A 17482-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291862</v>
+        <v>133453990</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435734</v>
+        <v>435763</v>
       </c>
       <c r="R2" t="n">
-        <v>7008481</v>
+        <v>7008828</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291869</v>
+        <v>133453988</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435758</v>
+        <v>435918</v>
       </c>
       <c r="R3" t="n">
-        <v>7008887</v>
+        <v>7008767</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291867</v>
+        <v>121291860</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435854</v>
+        <v>435794</v>
       </c>
       <c r="R4" t="n">
-        <v>7008888</v>
+        <v>7008406</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291870</v>
+        <v>121291861</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435732</v>
+        <v>435739</v>
       </c>
       <c r="R5" t="n">
-        <v>7008877</v>
+        <v>7008457</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291865</v>
+        <v>121291862</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435922</v>
+        <v>435734</v>
       </c>
       <c r="R6" t="n">
-        <v>7008747</v>
+        <v>7008481</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1148,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291868</v>
+        <v>121291863</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435839</v>
+        <v>435716</v>
       </c>
       <c r="R7" t="n">
-        <v>7008879</v>
+        <v>7008523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291861</v>
+        <v>121291864</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435739</v>
+        <v>435737</v>
       </c>
       <c r="R8" t="n">
-        <v>7008457</v>
+        <v>7008573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,15 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291863</v>
+        <v>121291865</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435716</v>
+        <v>435922</v>
       </c>
       <c r="R9" t="n">
-        <v>7008523</v>
+        <v>7008747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,12 +1484,7 @@
         <v>121291866</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,15 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291864</v>
+        <v>121291867</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435737</v>
+        <v>435854</v>
       </c>
       <c r="R11" t="n">
-        <v>7008573</v>
+        <v>7008888</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1658,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291917</v>
+        <v>121291868</v>
       </c>
       <c r="B12" t="n">
-        <v>90743</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435788</v>
+        <v>435839</v>
       </c>
       <c r="R12" t="n">
-        <v>7008420</v>
+        <v>7008879</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133454001</v>
+        <v>121291869</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435804</v>
+        <v>435758</v>
       </c>
       <c r="R13" t="n">
-        <v>7008833</v>
+        <v>7008887</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,17 +1852,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133453990</v>
+        <v>121291870</v>
       </c>
       <c r="B14" t="n">
-        <v>91959</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1900,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435763</v>
+        <v>435732</v>
       </c>
       <c r="R14" t="n">
-        <v>7008828</v>
+        <v>7008877</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,12 +1954,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +1991,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133454012</v>
+        <v>133453998</v>
       </c>
       <c r="B15" t="n">
         <v>57975</v>
@@ -2081,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435699</v>
+        <v>435885</v>
       </c>
       <c r="R15" t="n">
-        <v>7008763</v>
+        <v>7008854</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2066,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2093,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133454003</v>
+        <v>133453999</v>
       </c>
       <c r="B16" t="n">
         <v>57975</v>
@@ -2183,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435870</v>
+        <v>435882</v>
       </c>
       <c r="R16" t="n">
-        <v>7008629</v>
+        <v>7008846</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,7 +2195,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133454016</v>
+        <v>133454000</v>
       </c>
       <c r="B17" t="n">
         <v>57975</v>
@@ -2285,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435987</v>
+        <v>435871</v>
       </c>
       <c r="R17" t="n">
-        <v>7008739</v>
+        <v>7008840</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2270,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,7 +2297,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133454013</v>
+        <v>133454001</v>
       </c>
       <c r="B18" t="n">
         <v>57975</v>
@@ -2387,7 +2332,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435763</v>
+        <v>435804</v>
       </c>
       <c r="R18" t="n">
         <v>7008833</v>
@@ -2427,7 +2372,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,7 +2501,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133454000</v>
+        <v>133454003</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2591,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435871</v>
+        <v>435870</v>
       </c>
       <c r="R20" t="n">
-        <v>7008840</v>
+        <v>7008629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,7 +2576,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,7 +2705,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133453998</v>
+        <v>133454006</v>
       </c>
       <c r="B22" t="n">
         <v>57975</v>
@@ -2795,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435885</v>
+        <v>435721</v>
       </c>
       <c r="R22" t="n">
-        <v>7008854</v>
+        <v>7008628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,7 +2780,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,7 +2807,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133454018</v>
+        <v>133454011</v>
       </c>
       <c r="B23" t="n">
         <v>57975</v>
@@ -2897,10 +2842,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435984</v>
+        <v>435698</v>
       </c>
       <c r="R23" t="n">
-        <v>7008674</v>
+        <v>7008743</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2882,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2964,7 +2909,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133454017</v>
+        <v>133454012</v>
       </c>
       <c r="B24" t="n">
         <v>57975</v>
@@ -2999,10 +2944,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435994</v>
+        <v>435699</v>
       </c>
       <c r="R24" t="n">
-        <v>7008718</v>
+        <v>7008763</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3066,7 +3011,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133454014</v>
+        <v>133454013</v>
       </c>
       <c r="B25" t="n">
         <v>57975</v>
@@ -3101,10 +3046,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435769</v>
+        <v>435763</v>
       </c>
       <c r="R25" t="n">
-        <v>7008843</v>
+        <v>7008833</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3086,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,7 +3113,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133454006</v>
+        <v>133454014</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3203,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435721</v>
+        <v>435769</v>
       </c>
       <c r="R26" t="n">
-        <v>7008628</v>
+        <v>7008843</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,7 +3188,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3270,7 +3215,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133453999</v>
+        <v>133454016</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3305,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435882</v>
+        <v>435987</v>
       </c>
       <c r="R27" t="n">
-        <v>7008846</v>
+        <v>7008739</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,7 +3290,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,32 +3317,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133453988</v>
+        <v>133454017</v>
       </c>
       <c r="B28" t="n">
-        <v>91922</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3352,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435918</v>
+        <v>435994</v>
       </c>
       <c r="R28" t="n">
-        <v>7008767</v>
+        <v>7008718</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,6 +3388,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3469,7 +3419,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133454011</v>
+        <v>133454018</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3504,10 +3454,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435698</v>
+        <v>435984</v>
       </c>
       <c r="R29" t="n">
-        <v>7008743</v>
+        <v>7008674</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,7 +3494,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3568,6 +3518,103 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133454058</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110023</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220263</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fjällskråp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Petasites frigidus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>435674</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7008545</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17482-2026 artfynd.xlsx
+++ b/artfynd/A 17482-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453990</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453988</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291860</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291861</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291862</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291863</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291864</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291865</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291866</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291867</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291868</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291869</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291870</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453998</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453999</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454000</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2396,6 +2481,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454001</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2498,6 +2588,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454002</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2600,6 +2695,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454003</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454005</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2804,6 +2909,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454006</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2906,6 +3016,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454011</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3008,6 +3123,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454012</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3110,6 +3230,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454013</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3212,6 +3337,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454014</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3314,6 +3444,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454016</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3416,6 +3551,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454017</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3518,6 +3658,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454018</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3615,8 +3760,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454058</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>